--- a/dapan/cnttcb/Cau2.xlsx
+++ b/dapan/cnttcb/Cau2.xlsx
@@ -154,13 +154,37 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="22">
     <border>
@@ -450,7 +474,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -461,46 +485,49 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="4" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="4" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -798,15 +825,15 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" x14ac:dyDescent="0.4">
       <c r="A1" s="2"/>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="3"/>
     </row>
     <row r="2" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
@@ -821,226 +848,228 @@
       <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="13" t="s">
+      <c r="A3" s="10"/>
+      <c r="B3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="16"/>
+      <c r="I3" s="11"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="19">
+      <c r="A4" s="10"/>
+      <c r="B4" s="27">
         <v>1</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="20" t="str">
+      <c r="D4" s="18" t="str">
         <f>IF(RIGHT(C4,2)="TN","Trongnước",VLOOKUP(RIGHT(C4,2),$C$16:$D$20,2,0))</f>
         <v>Castrol</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <v>8200</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="33">
         <v>15000</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="21">
         <f>IF(RIGHT(C4,2)="TN","Miễn thuế",F4*E4*10%)</f>
         <v>12300000</v>
       </c>
-      <c r="H4" s="23">
+      <c r="H4" s="22">
         <f>IF(RIGHT(C4,2)="TN",F4*E4,E4*F4-G4)</f>
         <v>110700000</v>
       </c>
-      <c r="I4" s="16"/>
+      <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
-      <c r="B5" s="24">
+      <c r="A5" s="10"/>
+      <c r="B5" s="29">
         <v>2</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="25" t="str">
+      <c r="D5" s="19" t="str">
         <f t="shared" ref="D5:D10" si="0">IF(RIGHT(C5,2)="TN","Trongnước",VLOOKUP(RIGHT(C5,2),$C$16:$D$20,2,0))</f>
         <v>Mobil</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="34">
         <v>8200</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="34">
         <v>4000</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="23">
         <f t="shared" ref="G5:G10" si="1">IF(RIGHT(C5,2)="TN","Miễn thuế",F5*E5*10%)</f>
         <v>3280000</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="24">
         <f t="shared" ref="H5:H10" si="2">IF(RIGHT(C5,2)="TN",F5*E5,E5*F5-G5)</f>
         <v>29520000</v>
       </c>
-      <c r="I5" s="16"/>
+      <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="12"/>
-      <c r="B6" s="24">
+      <c r="A6" s="10"/>
+      <c r="B6" s="29">
         <v>3</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="25" t="str">
+      <c r="D6" s="19" t="str">
         <f t="shared" si="0"/>
         <v>British Petro</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="34">
         <v>8200</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="34">
         <v>3500</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="23">
         <f t="shared" si="1"/>
         <v>2870000</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="24">
         <f t="shared" si="2"/>
         <v>25830000</v>
       </c>
-      <c r="I6" s="16"/>
+      <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="12"/>
-      <c r="B7" s="24">
+      <c r="A7" s="10"/>
+      <c r="B7" s="29">
         <v>4</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="25" t="str">
+      <c r="D7" s="19" t="str">
         <f t="shared" si="0"/>
         <v>British Petro</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="34">
         <v>3500</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="34">
         <v>2000</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="23">
         <f t="shared" si="1"/>
         <v>700000</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="24">
         <f t="shared" si="2"/>
         <v>6300000</v>
       </c>
-      <c r="I7" s="16"/>
+      <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
-      <c r="B8" s="24">
+      <c r="A8" s="10"/>
+      <c r="B8" s="29">
         <v>5</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="25" t="str">
+      <c r="D8" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Esso</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="34">
         <v>3500</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="34">
         <v>3000</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="23">
         <f t="shared" si="1"/>
         <v>1050000</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="24">
         <f t="shared" si="2"/>
         <v>9450000</v>
       </c>
-      <c r="I8" s="16"/>
+      <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="24">
+      <c r="A9" s="10"/>
+      <c r="B9" s="29">
         <v>6</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="25" t="str">
+      <c r="D9" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Trongnước</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="34">
         <v>3500</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="34">
         <v>2000</v>
       </c>
-      <c r="G9" s="27" t="str">
+      <c r="G9" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Miễn thuế</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="24">
         <f t="shared" si="2"/>
         <v>7000000</v>
       </c>
-      <c r="I9" s="16"/>
+      <c r="I9" s="11"/>
     </row>
     <row r="10" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="12"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="30" t="s">
+      <c r="A10" s="10"/>
+      <c r="B10" s="31">
+        <v>7</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="30" t="str">
+      <c r="D10" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Shell</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="35">
         <v>4500</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="35">
         <v>2500</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="25">
         <f t="shared" si="1"/>
         <v>1125000</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10" s="26">
         <f t="shared" si="2"/>
         <v>10125000</v>
       </c>
-      <c r="I10" s="16"/>
+      <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="12"/>
+      <c r="A11" s="10"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -1048,10 +1077,10 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
-      <c r="I11" s="16"/>
+      <c r="I11" s="11"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
+      <c r="A12" s="10"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -1059,10 +1088,10 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
-      <c r="I12" s="16"/>
+      <c r="I12" s="11"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
+      <c r="A13" s="10"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -1070,110 +1099,110 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
-      <c r="I13" s="16"/>
+      <c r="I13" s="11"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="12"/>
+      <c r="A14" s="10"/>
       <c r="B14" s="5"/>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="10"/>
+      <c r="D14" s="13"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
-      <c r="I14" s="16"/>
+      <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="12"/>
+      <c r="A15" s="10"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="17" t="s">
         <v>15</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
-      <c r="I15" s="16"/>
+      <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="12"/>
+      <c r="A16" s="10"/>
       <c r="B16" s="5"/>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="36" t="s">
         <v>17</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
-      <c r="I16" s="16"/>
+      <c r="I16" s="11"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="12"/>
+      <c r="A17" s="10"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="36" t="s">
         <v>19</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
-      <c r="I17" s="16"/>
+      <c r="I17" s="11"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="12"/>
+      <c r="A18" s="10"/>
       <c r="B18" s="5"/>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="36" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
-      <c r="I18" s="16"/>
+      <c r="I18" s="11"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="12"/>
+      <c r="A19" s="10"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="36" t="s">
         <v>23</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
-      <c r="I19" s="16"/>
+      <c r="I19" s="11"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="12"/>
+      <c r="A20" s="10"/>
       <c r="B20" s="5"/>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="36" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
-      <c r="I20" s="16"/>
+      <c r="I20" s="11"/>
     </row>
     <row r="21" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7"/>

--- a/dapan/cnttcb/Cau2.xlsx
+++ b/dapan/cnttcb/Cau2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\New folder (7)\cb2310876\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (3)\quiz-search\dapan\cnttcb\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -487,12 +487,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -528,6 +522,12 @@
     <xf numFmtId="1" fontId="2" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="4" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -819,21 +819,21 @@
     <col min="5" max="5" width="12.81640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.1796875" style="1" customWidth="1"/>
     <col min="7" max="7" width="16.1796875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.54296875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.1796875" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20" x14ac:dyDescent="0.4">
       <c r="A1" s="2"/>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
       <c r="I1" s="3"/>
     </row>
     <row r="2" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
@@ -849,52 +849,52 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="10"/>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="14" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="11"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
-      <c r="B4" s="27">
+      <c r="B4" s="25">
         <v>1</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="18" t="str">
+      <c r="D4" s="16" t="str">
         <f>IF(RIGHT(C4,2)="TN","Trongnước",VLOOKUP(RIGHT(C4,2),$C$16:$D$20,2,0))</f>
         <v>Castrol</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="31">
         <v>8200</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="31">
         <v>15000</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="19">
         <f>IF(RIGHT(C4,2)="TN","Miễn thuế",F4*E4*10%)</f>
         <v>12300000</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="20">
         <f>IF(RIGHT(C4,2)="TN",F4*E4,E4*F4-G4)</f>
         <v>110700000</v>
       </c>
@@ -902,27 +902,27 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
-      <c r="B5" s="29">
+      <c r="B5" s="27">
         <v>2</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="19" t="str">
+      <c r="D5" s="17" t="str">
         <f t="shared" ref="D5:D10" si="0">IF(RIGHT(C5,2)="TN","Trongnước",VLOOKUP(RIGHT(C5,2),$C$16:$D$20,2,0))</f>
         <v>Mobil</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="32">
         <v>8200</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="32">
         <v>4000</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="21">
         <f t="shared" ref="G5:G10" si="1">IF(RIGHT(C5,2)="TN","Miễn thuế",F5*E5*10%)</f>
         <v>3280000</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="22">
         <f t="shared" ref="H5:H10" si="2">IF(RIGHT(C5,2)="TN",F5*E5,E5*F5-G5)</f>
         <v>29520000</v>
       </c>
@@ -930,27 +930,27 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="10"/>
-      <c r="B6" s="29">
+      <c r="B6" s="27">
         <v>3</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="19" t="str">
+      <c r="D6" s="17" t="str">
         <f t="shared" si="0"/>
         <v>British Petro</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="32">
         <v>8200</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="32">
         <v>3500</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="21">
         <f t="shared" si="1"/>
         <v>2870000</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="22">
         <f t="shared" si="2"/>
         <v>25830000</v>
       </c>
@@ -958,27 +958,27 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
-      <c r="B7" s="29">
+      <c r="B7" s="27">
         <v>4</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="19" t="str">
+      <c r="D7" s="17" t="str">
         <f t="shared" si="0"/>
         <v>British Petro</v>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="32">
         <v>3500</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="32">
         <v>2000</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="21">
         <f t="shared" si="1"/>
         <v>700000</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="22">
         <f t="shared" si="2"/>
         <v>6300000</v>
       </c>
@@ -986,27 +986,27 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
-      <c r="B8" s="29">
+      <c r="B8" s="27">
         <v>5</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="19" t="str">
+      <c r="D8" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Esso</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="32">
         <v>3500</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="32">
         <v>3000</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="21">
         <f t="shared" si="1"/>
         <v>1050000</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="22">
         <f t="shared" si="2"/>
         <v>9450000</v>
       </c>
@@ -1014,27 +1014,27 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
-      <c r="B9" s="29">
+      <c r="B9" s="27">
         <v>6</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="19" t="str">
+      <c r="D9" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Trongnước</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="32">
         <v>3500</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="32">
         <v>2000</v>
       </c>
-      <c r="G9" s="23" t="str">
+      <c r="G9" s="21" t="str">
         <f t="shared" si="1"/>
         <v>Miễn thuế</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="22">
         <f t="shared" si="2"/>
         <v>7000000</v>
       </c>
@@ -1042,27 +1042,27 @@
     </row>
     <row r="10" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
-      <c r="B10" s="31">
+      <c r="B10" s="29">
         <v>7</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="20" t="str">
+      <c r="D10" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Shell</v>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="33">
         <v>4500</v>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="33">
         <v>2500</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="23">
         <f t="shared" si="1"/>
         <v>1125000</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="24">
         <f t="shared" si="2"/>
         <v>10125000</v>
       </c>
@@ -1104,10 +1104,10 @@
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="5"/>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="13"/>
+      <c r="D14" s="36"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -1117,10 +1117,10 @@
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="15" t="s">
         <v>15</v>
       </c>
       <c r="E15" s="5"/>
@@ -1132,10 +1132,10 @@
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
       <c r="B16" s="5"/>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="36" t="s">
+      <c r="D16" s="34" t="s">
         <v>17</v>
       </c>
       <c r="E16" s="5"/>
@@ -1147,10 +1147,10 @@
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="36" t="s">
+      <c r="D17" s="34" t="s">
         <v>19</v>
       </c>
       <c r="E17" s="5"/>
@@ -1162,10 +1162,10 @@
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="10"/>
       <c r="B18" s="5"/>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="36" t="s">
+      <c r="D18" s="34" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="5"/>
@@ -1177,10 +1177,10 @@
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="10"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="36" t="s">
+      <c r="D19" s="34" t="s">
         <v>23</v>
       </c>
       <c r="E19" s="5"/>
@@ -1192,10 +1192,10 @@
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="10"/>
       <c r="B20" s="5"/>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="D20" s="34" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="5"/>
